--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.5607476635514018</v>
+        <v>0.711340206185567</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.6549295774647887</v>
       </c>
       <c r="D2">
-        <v>0.5419847328244275</v>
+        <v>0.4152542372881356</v>
       </c>
       <c r="E2">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F2">
+        <v>21</v>
+      </c>
+      <c r="G2">
         <v>24</v>
-      </c>
-      <c r="G2">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.711340206185567</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6549295774647887</v>
+        <v>0.6408450704225352</v>
       </c>
       <c r="D2">
-        <v>0.4152542372881356</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="E2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
